--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -19,6 +19,8 @@
     <sheet name="Choice" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="OpeningPresentation" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="OpeningLine" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Action" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="MapPosition" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1824,6 +1826,741 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>actionKey</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mustExecute</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>nameText</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>descText</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>requirements</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>resultEvents</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>durationDays</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>progressTarget</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>nextActionKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>行动唯一ID</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>行动类型</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>是否必须完成</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>名称文本key</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>描述文本key</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>需求表达式，分号分隔</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>完成后按顺序触发的Event ID，逗号分隔</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>时限天数</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>进度目标</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>后续行动key</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>act_meet_b</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>action.meet_b.name</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>action.meet_b.desc</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ActionPoint(1)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>EV_ACT_MEET</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>act_c_with_b</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>action.c_with_b.name</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>action.c_with_b.desc</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ActionPoint(1)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>EV_ACT_C_WITH_B</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>act_salon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ONCE</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>action.salon.name</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>action.salon.desc</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ActionPoint(1)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EV_ACT_SALON</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>act_peer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>REPEAT</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>action.peer.name</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>action.peer.desc</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ActionPoint(1)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>EV_ACT_C_PEER</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>positionKey</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>nameText</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>posX</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>posY</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>isImportant</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>defaultAction</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>extendedActions</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>imgPath</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>地点唯一ID</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>名称文本key</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>地图X</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>地图Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>是否重要地点</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>默认行动key</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>额外行动key，逗号分隔</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>图片路径</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>是否启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cafe</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>map.position.cafe.name</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-360</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>map.position.market.name</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>190</v>
+      </c>
+      <c r="E6" t="n">
+        <v>180</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>act_meet_b</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>map.position.library.name</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>420</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-220</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>temporary</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>map.position.temporary.name</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-120</v>
+      </c>
+      <c r="E8" t="n">
+        <v>300</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>act_c_with_b</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -2461,15 +2461,14 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-360</v>
+        <v>-1084.375</v>
       </c>
       <c r="E5" t="n">
-        <v>-80</v>
+        <v>445.9375</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="J5" t="b">
         <v>1</v>
       </c>
@@ -2486,10 +2485,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>190</v>
+        <v>-189.6875</v>
       </c>
       <c r="E6" t="n">
-        <v>180</v>
+        <v>264.6875</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -2515,10 +2514,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>420</v>
+        <v>55.625</v>
       </c>
       <c r="E7" t="n">
-        <v>-220</v>
+        <v>-87.1875</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -2539,10 +2538,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-120</v>
+        <v>168.75</v>
       </c>
       <c r="E8" t="n">
-        <v>300</v>
+        <v>557.1875</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -21,6 +21,12 @@
     <sheet name="OpeningLine" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Action" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="MapPosition" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="PresentationIndex" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ConversationPage" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ConversationLine" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Notice" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="ReadingPage" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="ReadingLine" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2560,6 +2566,1164 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>presentationClass</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>logTag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>presentationClass</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>logTag</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TEST_CONVERSATION</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TEST_CONVERSATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TEST_READING</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TEST_READING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TEST_NOTICE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TEST_NOTICE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pageId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pageCondKeys</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pageBarConds</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>optionGroupKey</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>bgOverride</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bgmOverride</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pageId</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>pageCondKeys</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>pageBarConds</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>optionGroupKey</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>bgOverride</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>bgmOverride</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_conv_page_01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TEST_CONVERSATION</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_conv_page_02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TEST_CONVERSATION</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>lineId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pageId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>speakerKey</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>textKey</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>voiceKey</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>emote</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sfxKey</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>accentFxKey</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>accentTargetKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lineId</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pageId</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>speakerKey</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>textKey</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>voiceKey</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>emote</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>sfxKey</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>accentFxKey</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>accentTargetKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_conv_line_01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>test_conv_page_01</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>narrative.test.conversation.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_conv_line_02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>test_conv_page_01</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>npc_a</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>narrative.test.conversation.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test_conv_line_03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>test_conv_page_02</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>npc_a</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>narrative.test.conversation.03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>titleKey</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>timeKey</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>imageKey</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>textKey</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>barConds</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>noticeBarConds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>titleKey</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>timeKey</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>imageKey</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>textKey</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>barConds</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>noticeBarConds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TEST_NOTICE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>narrative.test.notice.title</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>narrative.test.notice.body</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pageId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>titleKey</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>imageKey</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pageCondKeys</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pageBarConds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pageId</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>titleKey</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>imageKey</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>pageCondKeys</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>pageBarConds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_read_page_01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TEST_READING</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>narrative.test.reading.title</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_read_page_02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TEST_READING</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>narrative.test.reading.title</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3508,6 +4672,243 @@
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="n">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>lineId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pageId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>speakerKey</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>textKey</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>voiceKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lineId</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pageId</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>speakerKey</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>textKey</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>voiceKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_read_line_01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>test_read_page_01</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>narrative.test.reading.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_read_line_02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>test_read_page_02</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>npc_a</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>narrative.test.reading.02</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4393,7 +5794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5609,6 +7010,111 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>MUSICIAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EV_TEST_CONVERSATION</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>npc_a</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>narrative.test.conversation.title</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>TEST_CONVERSATION</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>TEST_CONVERSATION</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>TEST_CONVERSATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EV_TEST_READING</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>TEST_READING</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>TEST_READING</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>TEST_READING</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EV_TEST_NOTICE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>TEST_NOTICE</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>TEST_NOTICE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>TEST_NOTICE</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -472,324 +472,1416 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>objId</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>objType</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>nameText</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>iconPath</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>portraitPath</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>portraitIndoorPath</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>avtarPath</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>descText</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>objId</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>objType</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>nameText</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>iconPath</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>portraitPath</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>portraitIndoorPath</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>avtarPath</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>descText</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>npc_a</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>npc</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>npc.a.name</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>npc.a.desc</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>servant,poor,revolutionary</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>servant,poor,revolutionary,test_fixture</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>npc</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>npc.b.name</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>npc.b.desc</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>noble,daughter,love</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>noble,daughter,love,test_fixture</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>npc_c</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>npc</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>npc.c.name</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>npc.c.desc</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>noble,suitor,bourgeois</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>noble,suitor,bourgeois,test_fixture</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>npc_d</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>npc</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>npc.d.name</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>npc.d.desc</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>noble,father,authority</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>noble,father,authority,test_fixture</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>player.name</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>player.desc</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>observer</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>world.name</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>world.desc</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>world,ordia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>laurent</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>character.laurent.name</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>character.laurent.desc</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>noble,auditor,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>clovis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>character.clovis.name</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>character.clovis.desc</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>noble,king,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>renaud</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>character.renaud.name</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>character.renaud.desc</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>noble,duke,royal_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>elion</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>character.elion.name</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Characters/elion/neutral</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Characters/elion/neutral</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>character.elion.desc</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>noble,duke,crown,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>alienor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>character.alienor.name</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Characters/alienor/neutral</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Characters/alienor/indoor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Characters/alienor/neutral</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>character.alienor.desc</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>noble,princess,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>character.queen.name</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>character.queen.desc</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>noble,queen,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bertrand</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>character.bertrand.name</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Characters/bertrand/neutral</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Characters/bertrand/neutral</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>character.bertrand.desc</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>noble</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sade</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>character.sade.name</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Characters/sade/neutral</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Characters/sade/neutral</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>character.sade.desc</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>church,priest,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>mamion</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>character.mamion.name</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>character.mamion.desc</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>church,archbishop</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lucien</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>character.lucien.name</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>character.lucien.desc</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>church,priest</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>lesou</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>character.lesou.name</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Characters/lesou/neutral</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Characters/lesou/neutral</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>character.lesou.desc</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>refugee,revolution,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sylvain</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>character.sylvain.name</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>character.sylvain.desc</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>scholar,historian</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>antoine</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>character.antoine.name</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Characters/antoine/neutral</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Characters/antoine/neutral</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>character.antoine.desc</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>merchant,citizen,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>lefebvre</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>character.lefebvre.name</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>character.lefebvre.desc</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>official,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>duval</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>character.duval.name</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>character.duval.desc</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>citizen,uncle</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>character.adele.name</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Characters/adele/neutral</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Characters/adele/neutral</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>character.adele.desc</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>citizen,cafe_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>emmanuel</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>character.emmanuel.name</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>character.emmanuel.desc</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>citizen,surgeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sparrow</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>character.sparrow.name</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>character.sparrow.desc</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>citizen,street_youth</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>thibaut</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>character.thibaut.name</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Characters/thibaut/neutral</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Characters/thibaut/neutral</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>character.thibaut.desc</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>veteran,informant,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>octave</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>character.octave.name</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>character.octave.desc</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>military,general</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>eugene</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>character.eugene.name</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Characters/eugene/neutral</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Characters/eugene/neutral</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>character.eugene.desc</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>veteran,bodyguard,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>character.colette.name</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>character.colette.desc</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>citizen,cafe_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>character.pascal.name</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>character.pascal.desc</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>citizen,printer,cafe_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>marie</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>character.marie.name</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>character.marie.desc</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>citizen,former_manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>guest_a</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>character.guest_a.name</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>character.guest_a.desc</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>refugee,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>guest_b</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>character.guest_b.name</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>character.guest_b.desc</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>citizen,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>guest_c</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>character.guest_c.name</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>character.guest_c.desc</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>church,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>guest_d</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>character.guest_d.name</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>character.guest_d.desc</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>crown,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>soldier_a</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>character.soldier_a.name</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>character.soldier_a.desc</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>revolution,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>soldier_b</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>character.soldier_b.name</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>character.soldier_b.desc</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>military,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>soldier_c</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>character.soldier_c.name</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>character.soldier_c.desc</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>royal_guard,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>soldier_d</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>character.soldier_d.name</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>character.soldier_d.desc</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>new_rose,generic</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -472,37 +472,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>objId</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>objType</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nameText</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>iconPath</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>portraitPath</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>portraitIndoorPath</t>
         </is>
@@ -524,37 +524,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -576,37 +576,37 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -628,37 +628,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>objId</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>objType</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>nameText</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>iconPath</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>portraitPath</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>portraitIndoorPath</t>
         </is>
@@ -680,31 +680,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>npc_a</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>npc</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>npc.a.name</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>npc.a.desc</t>
@@ -712,36 +706,30 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>servant,poor,revolutionary,test_fixture</t>
+          <t>servant,poor,revolutionary</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>npc</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>npc.b.name</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>npc.b.desc</t>
@@ -749,36 +737,30 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>noble,daughter,love,test_fixture</t>
+          <t>noble,daughter,love</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>npc_c</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>npc</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>npc.c.name</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>npc.c.desc</t>
@@ -786,36 +768,30 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>noble,suitor,bourgeois,test_fixture</t>
+          <t>noble,suitor,bourgeois</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>npc_d</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>npc</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>npc.d.name</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>npc.d.desc</t>
@@ -823,31 +799,30 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>noble,father,authority,test_fixture</t>
+          <t>noble,father,authority</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>player.name</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>player.desc</t>
@@ -860,21 +835,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>world.name</t>
         </is>
       </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>world.desc</t>
@@ -883,1005 +862,6 @@
       <c r="J10" t="inlineStr">
         <is>
           <t>world,ordia</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>laurent</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>character.laurent.name</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>character.laurent.desc</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>noble,auditor,crown</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>clovis</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>character.clovis.name</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>character.clovis.desc</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>noble,king,crown</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>renaud</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>character.renaud.name</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>character.renaud.desc</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>noble,duke,royal_guard</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>elion</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>character.elion.name</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Characters/elion/neutral</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Characters/elion/neutral</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>character.elion.desc</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>noble,duke,crown,cafe_customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>alienor</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>character.alienor.name</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Characters/alienor/neutral</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Characters/alienor/indoor</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Characters/alienor/neutral</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>character.alienor.desc</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>noble,princess,crown</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>queen</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>character.queen.name</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>character.queen.desc</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>noble,queen,crown</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>bertrand</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>character.bertrand.name</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Characters/bertrand/neutral</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Characters/bertrand/neutral</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>character.bertrand.desc</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>noble</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>sade</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>character.sade.name</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Characters/sade/neutral</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Characters/sade/neutral</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>character.sade.desc</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>church,priest,cafe_customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>mamion</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>character.mamion.name</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>character.mamion.desc</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>church,archbishop</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>lucien</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>character.lucien.name</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>character.lucien.desc</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>church,priest</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>lesou</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>character.lesou.name</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Characters/lesou/neutral</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Characters/lesou/neutral</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>character.lesou.desc</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>refugee,revolution,cafe_customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>sylvain</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>character.sylvain.name</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>character.sylvain.desc</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>scholar,historian</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>antoine</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>character.antoine.name</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Characters/antoine/neutral</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Characters/antoine/neutral</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>character.antoine.desc</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>merchant,citizen,cafe_customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>lefebvre</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>character.lefebvre.name</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>character.lefebvre.desc</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>official,crown</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>duval</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>character.duval.name</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>character.duval.desc</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>citizen,uncle</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>adele</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>character.adele.name</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Characters/adele/neutral</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Characters/adele/neutral</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>character.adele.desc</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>citizen,cafe_staff</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>emmanuel</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>character.emmanuel.name</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>character.emmanuel.desc</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>citizen,surgeon</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sparrow</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>character.sparrow.name</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>character.sparrow.desc</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>citizen,street_youth</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>thibaut</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>character.thibaut.name</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Characters/thibaut/neutral</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Characters/thibaut/neutral</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>character.thibaut.desc</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>veteran,informant,cafe_customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>octave</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>character.octave.name</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>character.octave.desc</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>military,general</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>eugene</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>character.eugene.name</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Characters/eugene/neutral</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Characters/eugene/neutral</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>character.eugene.desc</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>veteran,bodyguard,cafe_customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>colette</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>character.colette.name</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>character.colette.desc</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>citizen,cafe_staff</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>pascal</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>character.pascal.name</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>character.pascal.desc</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>citizen,printer,cafe_staff</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>marie</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>character.marie.name</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>character.marie.desc</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>citizen,former_manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>guest_a</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>character.guest_a.name</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>character.guest_a.desc</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>refugee,generic</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>guest_b</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>character.guest_b.name</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>character.guest_b.desc</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>citizen,generic</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>guest_c</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>character.guest_c.name</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>character.guest_c.desc</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>church,generic</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>guest_d</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>character.guest_d.name</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>character.guest_d.desc</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>crown,generic</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>soldier_a</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>character.soldier_a.name</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>character.soldier_a.desc</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>revolution,generic</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>soldier_b</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>character.soldier_b.name</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>character.soldier_b.desc</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>military,generic</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>soldier_c</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>character.soldier_c.name</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>character.soldier_c.desc</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>royal_guard,generic</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>soldier_d</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>character.soldier_d.name</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Art/UI/Avatars/Unknown</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>character.soldier_d.desc</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>new_rose,generic</t>
         </is>
       </c>
     </row>
@@ -3336,7 +2316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3513,12 +2493,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>地图X</t>
+          <t>地图中心为0，向右为正，范围-1200至1200</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>地图Y</t>
+          <t>地图中心为0，向上为正，范围-675至675</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3538,12 +2518,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>图片路径</t>
+          <t>Resources路径（不含扩展名），重要=建筑，次要=事件图标/头像</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>次要地点初始可见；重要地点始终显示</t>
         </is>
       </c>
     </row>
@@ -3559,13 +2539,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1084.375</v>
+        <v>-952.5</v>
       </c>
       <c r="E5" t="n">
-        <v>445.9375</v>
+        <v>373.4375</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Art/Map/Locations/location_03</t>
+        </is>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -3583,10 +2568,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-189.6875</v>
+        <v>-57.8125</v>
       </c>
       <c r="E6" t="n">
-        <v>264.6875</v>
+        <v>192.1875</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -3594,6 +2579,11 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>act_meet_b</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Art/Map/Locations/location_05</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -3612,14 +2602,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55.625</v>
+        <v>187.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-87.1875</v>
+        <v>-159.6875</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
@@ -3636,10 +2631,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>168.75</v>
+        <v>300.625</v>
       </c>
       <c r="E8" t="n">
-        <v>557.1875</v>
+        <v>484.6875</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -3649,7 +2644,157 @@
           <t>act_c_with_b</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
       <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>圣西尔万郊区</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>map.position.saint_sylvain.name</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-379.375</v>
+      </c>
+      <c r="E9" t="n">
+        <v>406.25</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Art/Map/Locations/location_02</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>圣徒街</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>map.position.saint_street.name</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>774.6875</v>
+      </c>
+      <c r="E10" t="n">
+        <v>399.0625</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Art/Map/Locations/location_03</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>首都法院</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>map.position.capital_court.name</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>567.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Art/Map/Locations/location_06</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>市政厅</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>map.position.city_hall.name</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-411.5625</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45.3125</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Art/Map/Locations/location_07</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>花园区</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>map.position.garden_district.name</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>610.9375</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-407.1875</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Art/Map/Locations/location_09</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -862,6 +862,1005 @@
       <c r="J10" t="inlineStr">
         <is>
           <t>world,ordia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>laurent</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>character.laurent.name</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>character.laurent.desc</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>noble,auditor,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>clovis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>character.clovis.name</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>character.clovis.desc</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>noble,king,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>renaud</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>character.renaud.name</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>character.renaud.desc</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>noble,duke,royal_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>elion</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>character.elion.name</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Characters/elion/neutral</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Characters/elion/neutral</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>character.elion.desc</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>noble,duke,crown,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>alienor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>character.alienor.name</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Characters/alienor/neutral</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Characters/alienor/indoor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Characters/alienor/neutral</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>character.alienor.desc</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>noble,princess,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>character.queen.name</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>character.queen.desc</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>noble,queen,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bertrand</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>character.bertrand.name</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Characters/bertrand/neutral</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Characters/bertrand/neutral</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>character.bertrand.desc</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>noble</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sade</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>character.sade.name</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Characters/sade/neutral</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Characters/sade/neutral</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>character.sade.desc</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>church,priest,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>mamion</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>character.mamion.name</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>character.mamion.desc</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>church,archbishop</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lucien</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>character.lucien.name</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>character.lucien.desc</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>church,priest</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>lesou</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>character.lesou.name</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Characters/lesou/neutral</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Characters/lesou/neutral</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>character.lesou.desc</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>refugee,revolution,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sylvain</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>character.sylvain.name</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>character.sylvain.desc</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>scholar,historian</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>antoine</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>character.antoine.name</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Characters/antoine/neutral</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Characters/antoine/neutral</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>character.antoine.desc</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>merchant,citizen,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>lefebvre</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>character.lefebvre.name</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>character.lefebvre.desc</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>official,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>duval</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>character.duval.name</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>character.duval.desc</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>citizen,uncle</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>character.adele.name</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Characters/adele/neutral</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Characters/adele/neutral</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>character.adele.desc</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>citizen,cafe_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>emmanuel</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>character.emmanuel.name</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>character.emmanuel.desc</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>citizen,surgeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sparrow</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>character.sparrow.name</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>character.sparrow.desc</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>citizen,street_youth</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>thibaut</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>character.thibaut.name</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Characters/thibaut/neutral</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Characters/thibaut/neutral</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>character.thibaut.desc</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>veteran,informant,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>octave</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>character.octave.name</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>character.octave.desc</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>military,general</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>eugene</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>character.eugene.name</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Characters/eugene/neutral</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Characters/eugene/neutral</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>character.eugene.desc</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>veteran,bodyguard,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>character.colette.name</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>character.colette.desc</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>citizen,cafe_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>character.pascal.name</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>character.pascal.desc</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>citizen,printer,cafe_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>marie</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>character.marie.name</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>character.marie.desc</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>citizen,former_manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>guest_a</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>character.guest_a.name</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>character.guest_a.desc</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>refugee,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>guest_b</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>character.guest_b.name</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>character.guest_b.desc</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>citizen,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>guest_c</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>character.guest_c.name</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>character.guest_c.desc</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>church,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>guest_d</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>character.guest_d.name</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>character.guest_d.desc</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>crown,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>soldier_a</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>character.soldier_a.name</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>character.soldier_a.desc</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>revolution,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>soldier_b</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>character.soldier_b.name</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>character.soldier_b.desc</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>military,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>soldier_c</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>character.soldier_c.name</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>character.soldier_c.desc</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>royal_guard,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>soldier_d</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>character.soldier_d.name</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Art/UI/Avatars/Unknown</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>character.soldier_d.desc</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>new_rose,generic</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -27,6 +27,13 @@
     <sheet name="Notice" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="ReadingPage" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="ReadingLine" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="ConditionKey" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="ActionMilestone" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Ending" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="CafeVisit" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="CafeVisitHook" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="AbilityCheck" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="AbilityCheckCondition" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -865,6 +872,75 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>character.adele.name</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Characters/adele/neutral</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Characters/adele/neutral</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Characters/adele/neutral</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Characters/adele/neutral</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>character.adele.desc</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>citizen,cafe_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cafe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>player.external.money</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cafe</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -876,7 +952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -918,6 +994,11 @@
           <t>seq</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>checkId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -950,6 +1031,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -982,6 +1068,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1012,6 +1103,11 @@
       <c r="F4" s="1" t="inlineStr">
         <is>
           <t>seq</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>checkId</t>
         </is>
       </c>
     </row>
@@ -1910,7 +2006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1969,6 +2065,11 @@
           <t>nextActionKey</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>deliveryMode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2026,6 +2127,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2083,6 +2189,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2140,6 +2251,11 @@
           <t>后续行动key</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>每日固定交付：None/Cumulative/Consecutive</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -2181,6 +2297,11 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -2222,6 +2343,11 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2263,6 +2389,11 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -2303,6 +2434,103 @@
       </c>
       <c r="J8" t="n">
         <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>act_test_delivery_cumulative</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PROGRESS</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>act_test_delivery_cumulative.name</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>act_test_delivery_cumulative.desc</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Item(medicine,2);Item(food,1);ActionPoint(1)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Cumulative</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>act_test_delivery_consecutive</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PROGRESS</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>act_test_delivery_consecutive.name</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>act_test_delivery_consecutive.desc</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Item(medicine,2);Item(food,1);ActionPoint(1)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Consecutive</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2809,7 +3037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2948,6 +3176,57 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>TEST_NOTICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_BEFORE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_SERVED</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_CHAT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
         </is>
       </c>
     </row>
@@ -2962,7 +3241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3181,6 +3460,51 @@
       </c>
       <c r="D6" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_BEFORE_PAGE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_BEFORE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_SERVED_PAGE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_SERVED</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_CHAT_PAGE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_CHAT</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3194,7 +3518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3532,6 +3856,96 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>narrative.test.conversation.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_BEFORE_LINE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_BEFORE_PAGE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>demo.cafe.before</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_SERVED_LINE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_SERVED_PAGE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>demo.cafe.served</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_CHAT_LINE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_CHAT_PAGE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>demo.cafe.chat</t>
         </is>
       </c>
     </row>
@@ -3967,7 +4381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4068,6 +4482,21 @@
           <t>autoStep</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>sourceMode</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>providerId</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>sourceKey</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -4150,6 +4579,21 @@
           <t>int</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -4232,6 +4676,21 @@
           <t>c</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4312,6 +4771,21 @@
       <c r="P4" s="1" t="inlineStr">
         <is>
           <t>autoStep</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>sourceMode</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>providerId</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>sourceKey</t>
         </is>
       </c>
     </row>
@@ -4366,6 +4840,11 @@
       <c r="P5" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -4422,6 +4901,11 @@
       <c r="P6" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -4478,6 +4962,11 @@
       <c r="P7" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -4534,6 +5023,11 @@
       <c r="P8" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -4590,6 +5084,11 @@
       <c r="P9" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -4646,6 +5145,11 @@
       <c r="P10" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -4698,6 +5202,11 @@
       <c r="P11" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -4750,6 +5259,11 @@
       <c r="P12" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -4806,6 +5320,11 @@
       <c r="P13" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -4858,6 +5377,11 @@
       <c r="P14" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -4890,7 +5414,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>monotonic</t>
+          <t>event_driven</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
@@ -4908,7 +5432,416 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>dayflow</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cafe</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2147483647</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>highIsGood</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>event_driven</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>player.external.money</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>cafe</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>action_points</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2147483647</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>highIsGood</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>event_driven</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>player.external.action_points</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>actions</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>action_points_max</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2147483647</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>highIsGood</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>event_driven</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>player.external.action_points_max</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>actions</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>highIsGood</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>event_driven</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>player.attribute.language</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>courage</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>highIsGood</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>event_driven</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>player.attribute.courage</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wisdom</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>highIsGood</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>event_driven</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>player.attribute.wisdom</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>perception</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>highIsGood</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>event_driven</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>player.attribute.perception</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5146,6 +6079,1762 @@
         <is>
           <t>narrative.test.reading.02</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>nameText</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>initialValue</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>onlySetTrue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nameText</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>initialValue</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>onlySetTrue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>a_educated</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>condition.a_educated</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ab_swear</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>condition.ab_swear</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>accepted_tea</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>condition.accepted_tea</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>b_arrested</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>condition.b_arrested</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>bc_swear</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>condition.bc_swear</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>comrade</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>condition.comrade</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>eloped</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>condition.eloped</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fled</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>condition.fled</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>met_in_secret</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>condition.met_in_secret</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>musician_end</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>condition.musician_end</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>npc.npc_b.dead</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>condition.npc.npc_b.dead</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>player_influence</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>condition.player_influence</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>revolution</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>condition.revolution</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>specialization.player.letter.literature</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>condition.specialization.player.letter.literature</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>specialization.player.letter.politics</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>condition.specialization.player.letter.politics</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>specialization.player.letter.religion</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>condition.specialization.player.letter.religion</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>specialization.player.letter.science</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>condition.specialization.player.letter.science</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>standoff_done</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>condition.standoff_done</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>test.delivery.enabled</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>condition.test.delivery.enabled</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>demo.cafe.leaving</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>demo.cafe.leaving</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>demo.cafe.ended</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>demo.cafe.ended</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>milestoneId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>actionKey</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>atProgress</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eventId</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>milestoneId</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>actionKey</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>atProgress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>eventId</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>act_test_delivery_cumulative.two</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>act_test_delivery_cumulative</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>act_test_delivery_consecutive.two</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>act_test_delivery_consecutive</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>endingId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>titleText</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>messageText</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>endingId</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>titleText</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>messageText</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ending_test_cumulative</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ending_test_cumulative.title</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ending_test_cumulative.message</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ending_test_consecutive</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ending_test_consecutive.title</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ending_test_consecutive.message</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>visitKey</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>characterId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>preferredSeatId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>seatedVisualPath</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrivalDelaySeconds</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>patienceSeconds</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>leaveAfterServed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>visitKey</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>characterId</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>preferredSeatId</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>seatedVisualPath</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>arrivalDelaySeconds</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>patienceSeconds</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>leaveAfterServed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>demo_cafe_visit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>customer_0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>demo_cafe_delayed_visit</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>customer_0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>visitKey</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eventId</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>visitKey</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>eventId</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>demo_cafe_visit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>before_served</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>click</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>demo_cafe_visit</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>served</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_SERVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>demo_cafe_visit</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>served</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>click</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_CHAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>demo_cafe_visit</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>leaving</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_LEAVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>demo_cafe_visit</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_ENDED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>checkId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>successEventId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>failureEventId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>successResultOwnerId</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>failureResultOwnerId</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>checkId</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>successEventId</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>failureEventId</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>successResultOwnerId</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>failureResultOwnerId</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>策划备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>first_day_perception</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EV_FIRST_DAY_PERCEPTION_SUCCESS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EV_FIRST_DAY_PERCEPTION_FAILURE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>首日顾客B；知觉达到3触发成功支线</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>conditionId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>checkId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attributeId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>groupIndex</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>conditionId</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>checkId</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>attributeId</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>groupIndex</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>first_day_perception_001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>first_day_perception</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>perception</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6031,7 +8720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7352,6 +10041,546 @@
       <c r="N25" t="inlineStr">
         <is>
           <t>TEST_NOTICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE.title</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE.body</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Tpl_WorldBroadcast</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE</t>
+        </is>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>CONDITION_TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.title</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.body</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Tpl_WorldBroadcast</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>CONDITION_TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE.title</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE.body</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Tpl_WorldBroadcast</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE</t>
+        </is>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>CONDITION_TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.title</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.body</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Tpl_WorldBroadcast</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE</t>
+        </is>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>CONDITION_TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_RESERVE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_DELAYED_RESERVE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_ARRIVE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_CANCEL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_BEFORE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_SERVED</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_SERVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_CHAT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>DEMO_CAFE_CHAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_LEAVING</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO_LEAVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_ENDED</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>CAFE_VISIT_DEMO_ENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EV_FIRST_DAY_PERCEPTION_CHECK</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>first_day_perception_check</t>
+        </is>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>FIRST_DAY_PERCEPTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EV_FIRST_DAY_PERCEPTION_SUCCESS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>first.day.perception.success</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>first_day_perception_success</t>
+        </is>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>FIRST_DAY_PERCEPTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EV_FIRST_DAY_PERCEPTION_FAILURE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>first.day.perception.failure</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>first_day_perception_failure</t>
+        </is>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>FIRST_DAY_PERCEPTION</t>
         </is>
       </c>
     </row>
@@ -7564,7 +10793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7947,7 +11176,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>flag:met_in_secret</t>
+          <t>met_in_secret</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8199,7 +11428,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>flag:a_educated</t>
+          <t>a_educated</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8271,7 +11500,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>flag:ab_swear</t>
+          <t>ab_swear</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8415,7 +11644,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>flag:bc_swear</t>
+          <t>bc_swear</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8559,7 +11788,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>flag:standoff_done</t>
+          <t>standoff_done</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8631,7 +11860,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>flag:comrade</t>
+          <t>comrade</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8703,7 +11932,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>flag:b_arrested</t>
+          <t>b_arrested</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8811,7 +12040,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>flag:b_arrested</t>
+          <t>b_arrested</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9063,7 +12292,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>flag:eloped</t>
+          <t>eloped</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9135,7 +12364,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>flag:fled</t>
+          <t>fled</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -9207,7 +12436,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>flag:revolution</t>
+          <t>revolution</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -9279,7 +12508,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>flag:musician_end</t>
+          <t>musician_end</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -9422,7 +12651,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>flag:accepted_tea</t>
+          <t>accepted_tea</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -9433,6 +12662,281 @@
       <c r="H51" t="inlineStr">
         <is>
           <t>接受茶杯</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>R_EV_TEST_DELIVERY_CUMULATIVE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ITEM_ADD</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>delivery_receipt</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>只奖励收据，不重复扣交付成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>R_EV_TEST_DELIVERY_CONSECUTIVE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ITEM_ADD</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>delivery_receipt</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>只奖励收据，不重复扣交付成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>R_DEMO_CAFE_RESERVE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_RESERVE</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RESERVE_CAFE_VISIT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>obj:adele</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>visit:demo_cafe_visit</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>特殊来访测试入口；不自动挂入正式日历</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>R_DEMO_CAFE_DELAYED_RESERVE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_DELAYED_RESERVE</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RESERVE_CAFE_VISIT</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>obj:adele</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>visit:demo_cafe_delayed_visit</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>特殊来访测试入口；不自动挂入正式日历</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>R_DEMO_CAFE_ARRIVE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_ARRIVE</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SPAWN_NPC</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>obj:adele</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>scene:cafe</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>特殊来访测试入口；不自动挂入正式日历</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>R_DEMO_CAFE_CANCEL</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_CANCEL</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DESPAWN_NPC</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>obj:adele</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>特殊来访测试入口；不自动挂入正式日历</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>R_DEMO_CAFE_LEAVING</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_LEAVING</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SET_FLAG</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>demo.cafe.leaving</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>示例阶段反馈可查看条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>R_DEMO_CAFE_ENDED</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EV_DEMO_CAFE_ENDED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SET_FLAG</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>demo.cafe.ended</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>示例阶段反馈可查看条件</t>
         </is>
       </c>
     </row>
@@ -9447,7 +12951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9500,17 +13004,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>op</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>value</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>notFlag</t>
         </is>
       </c>
     </row>
@@ -9555,16 +13049,6 @@
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -9607,16 +13091,6 @@
           <t>c</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -9656,17 +13130,7 @@
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>op</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
           <t>value</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>notFlag</t>
         </is>
       </c>
     </row>
@@ -9700,17 +13164,10 @@
           <t>event:EV_BC_SWEAR</t>
         </is>
       </c>
-      <c r="H5" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
-      </c>
-      <c r="J5" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -9743,17 +13200,10 @@
           <t>event:EV_AB_SWEAR</t>
         </is>
       </c>
-      <c r="H6" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
-      </c>
-      <c r="J6" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9788,16 +13238,8 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
           <t>8</t>
         </is>
-      </c>
-      <c r="J7" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9832,16 +13274,8 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="J8" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -9876,16 +13310,8 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
           <t>8</t>
         </is>
-      </c>
-      <c r="J9" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -9920,16 +13346,8 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="J10" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -9962,17 +13380,10 @@
           <t>event:EV_BC_SWEAR</t>
         </is>
       </c>
-      <c r="H11" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
-      </c>
-      <c r="J11" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -10007,16 +13418,8 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
           <t>5</t>
         </is>
-      </c>
-      <c r="J12" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -10051,16 +13454,8 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="J13" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -10093,17 +13488,10 @@
           <t>event:EV_AB_SWEAR</t>
         </is>
       </c>
-      <c r="H14" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
-      </c>
-      <c r="J14" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -10136,17 +13524,10 @@
           <t>event:EV_BC_SWEAR</t>
         </is>
       </c>
-      <c r="H15" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
-      </c>
-      <c r="J15" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -10179,17 +13560,10 @@
           <t>event:EV_AB_SWEAR</t>
         </is>
       </c>
-      <c r="H16" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
-      </c>
-      <c r="J16" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -10224,16 +13598,8 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
           <t>5</t>
         </is>
-      </c>
-      <c r="J17" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10258,25 +13624,18 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>FLAG_SET</t>
+          <t>BOOL_EQ</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>flag:player_influence</t>
-        </is>
-      </c>
-      <c r="H18" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+          <t>player_influence</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
-      </c>
-      <c r="J18" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10309,17 +13668,10 @@
           <t>event:EV_AB_SWEAR</t>
         </is>
       </c>
-      <c r="H19" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
-      </c>
-      <c r="J19" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -10352,17 +13704,10 @@
           <t>event:EV_BC_SWEAR</t>
         </is>
       </c>
-      <c r="H20" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
-      </c>
-      <c r="J20" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -10387,25 +13732,148 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>FLAG_SET</t>
+          <t>BOOL_EQ</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>flag:a_educated</t>
-        </is>
-      </c>
-      <c r="H21" s="2">
-        <f>=</f>
-        <v/>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+          <t>a_educated</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J21" s="2" t="b">
-        <v>0</v>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C_act_test_delivery_cumulative</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>act_test_delivery_cumulative</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BOOL_EQ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>test.delivery.enabled</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C_ending_test_cumulative</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ending_test_cumulative</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ACTION_COMPLETED</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>act_test_delivery_cumulative</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C_act_test_delivery_consecutive</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>act_test_delivery_consecutive</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BOOL_EQ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>test.delivery.enabled</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C_ending_test_consecutive</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ending_test_consecutive</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ACTION_COMPLETED</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>act_test_delivery_consecutive</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -10869,7 +14337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10911,6 +14379,11 @@
           <t>autoAdvance</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>checkId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -10943,6 +14416,11 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -10975,6 +14453,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -11005,6 +14488,11 @@
       <c r="F4" s="1" t="inlineStr">
         <is>
           <t>autoAdvance</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>checkId</t>
         </is>
       </c>
     </row>
@@ -11437,6 +14925,167 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tpl_WorldBroadcast</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>titleKey=EV_TEST_DELIVERY_CUMULATIVE.title,lines=EV_TEST_DELIVERY_CUMULATIVE.body</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tpl_WorldBroadcast</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>titleKey=EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.title,lines=EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.body</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tpl_WorldBroadcast</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>titleKey=EV_TEST_DELIVERY_CONSECUTIVE.title,lines=EV_TEST_DELIVERY_CONSECUTIVE.body</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tpl_WorldBroadcast</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>titleKey=EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.title,lines=EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.body</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>first_day_perception_check</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>first_day_perception</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>first_day_perception_success</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>titleKey=first.day.perception.success.title,lines=first.day.perception.success</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>first_day_perception_failure</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>titleKey=first.day.perception.failure.title,lines=first.day.perception.failure</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -34,6 +34,7 @@
     <sheet name="CafeVisitHook" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="AbilityCheck" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="AbilityCheckCondition" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="CafeTutorialStep" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1226,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1260,6 +1261,11 @@
           <t>visualsResource</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>centerNameKey</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1292,6 +1298,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1324,6 +1335,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1356,6 +1372,11 @@
           <t>visualsResource</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>第三角色显示名</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -1381,6 +1402,779 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.customer_arrives</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.title</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.title</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_failure</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_failure.title</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.order_confirmed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.title</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.workstation_open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.workstation_open.title</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.make_coffee_base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.make_coffee_base.title</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.pour_into_cup</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.pour_into_cup.title</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.adjust_strength</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_strength.title</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.adjust_sweetness</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_sweetness.title</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_grind</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_grind.title</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_boil</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_boil.title</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_brew</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_brew.title</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_cup</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_cup.title</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_base</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_base.title</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_strength</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_strength.title</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_sweetness</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_sweetness.title</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_serve</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_serve.title</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.serve_customer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.serve_customer.title</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_excellent</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_excellent.title</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_good</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_good.title</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_average</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_average.title</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_bad</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_bad.title</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_refund</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_refund.title</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.ending</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.title</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>opening.player.name</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>opening.adele.name</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
         </is>
       </c>
     </row>
@@ -1395,7 +2189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,7 +2363,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>opening_01</t>
+          <t>opening_001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1582,7 +2376,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>narrator</t>
+          <t>right</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1602,7 +2396,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>opening_02</t>
+          <t>opening_002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1625,7 +2419,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nod</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1635,7 +2429,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>opening_03</t>
+          <t>opening_003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1648,7 +2442,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1668,7 +2462,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>opening_04</t>
+          <t>opening_004</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1701,7 +2495,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>opening_05</t>
+          <t>opening_005</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1714,7 +2508,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>narrator</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1734,7 +2528,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>opening_06</t>
+          <t>opening_006</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1747,7 +2541,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>narrator</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1767,7 +2561,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>opening_07</t>
+          <t>opening_007</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1780,7 +2574,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1800,7 +2594,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>opening_08</t>
+          <t>opening_008</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1813,7 +2607,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>narrator</t>
+          <t>right</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1833,30 +2627,30 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>opening_09</t>
+          <t>cafe_tutorial_001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>first_day_cafe</t>
+          <t>cafe_tutorial.customer_arrives</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>narrator</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>opening.line.09</t>
+          <t>cafe.tutorial.customer_arrives.01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>nod</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1866,25 +2660,25 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>opening_10</t>
+          <t>cafe_tutorial_002</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>first_day_cafe</t>
+          <t>cafe_tutorial.customer_arrives</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>opening.line.10</t>
+          <t>cafe.tutorial.customer_arrives.02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1899,16 +2693,16 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>opening_11</t>
+          <t>cafe_tutorial_003</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>first_day_cafe</t>
+          <t>cafe_tutorial.customer_arrives</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1917,7 +2711,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>opening.line.11</t>
+          <t>cafe.tutorial.customer_arrives.03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1932,25 +2726,25 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>opening_12</t>
+          <t>cafe_tutorial_004</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>first_day_cafe</t>
+          <t>cafe_tutorial.customer_arrives</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>opening.line.12</t>
+          <t>cafe.tutorial.customer_arrives.04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1965,33 +2759,1683 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>opening_13</t>
+          <t>cafe_tutorial_005</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>first_day_cafe</t>
+          <t>cafe_tutorial.customer_arrives</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_006</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.customer_arrives</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_007</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_008</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_009</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.03</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_010</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_011</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_012</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_013</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>right</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>opening.line.13</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>nod</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.07</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_014</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_015</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_016</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_failure</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_failure.01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_017</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_failure</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_failure.02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_018</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_failure</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_failure.03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_019</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.order_confirmed</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_020</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.order_confirmed</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.02</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_021</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.order_confirmed</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.03</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_022</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.order_confirmed</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_023</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.workstation_open</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.workstation_open.01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_024</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.make_coffee_base</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.make_coffee_base.01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_025</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.make_coffee_base</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.make_coffee_base.02</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.make_coffee_base</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.make_coffee_base.03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_027</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.pour_into_cup</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.pour_into_cup.01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_028</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.adjust_strength</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_strength.01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_029</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.adjust_sweetness</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_sweetness.01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_030</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.adjust_sweetness</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_sweetness.02</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_031</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_grind</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_grind.01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_032</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_boil</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_boil.01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_033</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_brew</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_brew.01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_034</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_cup</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_cup.01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_035</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_base</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_base.01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_036</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_strength</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_strength.01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_037</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_sweetness</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_sweetness.01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_038</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_serve</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_serve.01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_039</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.serve_customer</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.serve_customer.01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_040</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_excellent</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_excellent.01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_041</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_excellent</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_excellent.02</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_042</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_good</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_good.01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_043</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_good</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_good.02</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_044</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_average</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_average.01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_045</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_average</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_average.02</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_046</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_bad</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_bad.01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_047</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_bad</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_bad.02</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_048</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_refund</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_refund.01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_049</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_refund</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_refund.02</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_050</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.ending</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_051</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.ending</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.02</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_052</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.ending</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.03</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_053</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.ending</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.04</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_054</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.ending</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.05</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>cafe_tutorial_055</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.ending</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.06</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7842,6 +10286,855 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stepId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tutorialId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>presentationId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>focusTargetKey</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>completionSignalId</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>nextStepId</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>optionalDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>步骤</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>教程</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NCS段落</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>焦点</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>完成信号</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>后续步骤或分支标记</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>可选演示</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>introduction</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>first_day_cafe</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>customer_arrives</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>customer_arrives</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.customer_arrives</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>perception_check</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>perception_success</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_success</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>order_confirmed</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>perception_failure</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.perception_failure</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>order_confirmed</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>order_confirmed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.order_confirmed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>workstation_open</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>workstation_open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.workstation_open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>cafe.workstation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>workstation_opened</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>make_coffee_base</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>make_coffee_base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.make_coffee_base</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>cafe.coffee_base</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pour_into_cup</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pour_into_cup</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.pour_into_cup</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>cafe.cup</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>adjust_strength</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>adjust_strength</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.adjust_strength</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>cafe.strength</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>adjust_sweetness</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>adjust_sweetness</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.adjust_sweetness</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>cafe.sweetness</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>serve_customer</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>demo_grind</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_grind</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>demo_boil</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_boil</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>demo_brew</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_brew</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>demo_cup</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_cup</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>demo_base</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_base</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>demo_strength</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_strength</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>demo_sweetness</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_sweetness</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>demo_serve</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.demo_serve</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>serve_customer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.serve_customer</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>cafe.delivery</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>result_excellent</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_excellent</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>result_good</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_good</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>result_average</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_average</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>result_bad</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_bad</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>result_refund</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.result_refund</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>make_coffee_base</t>
+        </is>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>first_cafe_tutorial</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>cafe_tutorial.ending</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -10520,11 +13813,6 @@
           <t>world</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>first.day.perception.success</t>
-        </is>
-      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Tpl_Narration</t>
@@ -10558,11 +13846,6 @@
       <c r="D41" t="inlineStr">
         <is>
           <t>world</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>first.day.perception.failure</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -15054,11 +18337,6 @@
           <t>Tpl_Narration</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>titleKey=first.day.perception.success.title,lines=first.day.perception.success</t>
-        </is>
-      </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
@@ -15075,11 +18353,6 @@
       <c r="C29" t="inlineStr">
         <is>
           <t>Tpl_Narration</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>titleKey=first.day.perception.failure.title,lines=first.day.perception.failure</t>
         </is>
       </c>
       <c r="E29" t="b">

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -953,7 +953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1214,6 +1214,156 @@
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.1</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.2</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.1</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.2</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.1</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.2</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5481,7 +5631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,6 +5821,159 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>CAFE_VISIT_DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>arrival.start</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FIRST_ARRIVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>arrival.reply.1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FIRST_ARRIVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>arrival.reply.2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FIRST_ARRIVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>arrival.agent</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FIRST_ARRIVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>arrival.insight</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FIRST_ARRIVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>arrival.request</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FIRST_ARRIVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>arrival.decision</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FIRST_ARRIVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>arrival.refuse</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FIRST_ARRIVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>arrival.accept</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FIRST_ARRIVAL</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5950,6 +6253,162 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>arrival.start</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>arrival.reply.1.page</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>arrival.reply.1</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>arrival.reply.2.page</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>arrival.reply.2</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>arrival.agent.page</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>arrival.agent</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>arrival.insight.page</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>arrival.insight</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>arrival.request.page</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>arrival.request</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>arrival.decision.page</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>arrival.decision</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>arrival.refuse</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>arrival.accept</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5962,7 +6421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6392,6 +6851,1376 @@
           <t>demo.cafe.chat</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>arrival.start.01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>arrival.start.01</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>arrival.start.02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>arrival.start.02</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>arrival.start.03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>arrival.start.03</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>arrival.start.04</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>arrival.start.04</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>arrival.start.05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>arrival.start.05</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>arrival.start.06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>arrival.start.06</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>arrival.start.07</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>arrival.start.07</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>arrival.start.08</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>arrival.start.08</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>arrival.start.09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>arrival.start.09</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>arrival.start.10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>arrival.start.10</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>arrival.start.11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>arrival.start.11</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>平静</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>arrival.start.12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>arrival.start.12</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>arrival.start.13</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>arrival.start.page</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>arrival.start.13</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>开心</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>arrival.reply.1.01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>arrival.reply.1.page</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>arrival.reply.1.01</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>arrival.reply.2.01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>arrival.reply.2.page</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>arrival.reply.2.01</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>arrival.agent.01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>arrival.agent.page</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>arrival.agent.01</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>尴尬</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>arrival.agent.02</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>arrival.agent.page</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>arrival.agent.02</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>平静</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>arrival.agent.03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>arrival.agent.page</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>arrival.agent.03</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>arrival.agent.04</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>arrival.agent.page</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>arrival.agent.04</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>思索</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>arrival.insight.01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>arrival.insight.page</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>arrival.insight.01</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>arrival.request.01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>arrival.request.page</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>arrival.request.01</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>arrival.request.02</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>arrival.request.page</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>arrival.request.02</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>悲伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>arrival.request.03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>arrival.request.page</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>arrival.request.03</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>arrival.request.04</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>arrival.request.page</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>arrival.request.04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>焦虑</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>arrival.decision.01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>arrival.decision.page</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>arrival.decision.01</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>arrival.refuse.01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>arrival.refuse.01</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>arrival.refuse.02</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>arrival.refuse.02</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>arrival.refuse.03</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>arrival.refuse.03</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>arrival.refuse.04</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>arrival.refuse.04</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>arrival.refuse.05</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>arrival.refuse.05</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>arrival.refuse.06</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>arrival.refuse.06</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>arrival.refuse.07</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>arrival.refuse.07</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>arrival.refuse.08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>arrival.refuse.08</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>arrival.refuse.09</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>arrival.refuse.page</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>arrival.refuse.09</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>arrival.accept.01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>arrival.accept.01</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>arrival.accept.02</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>arrival.accept.02</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>迷惑</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>arrival.accept.03</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>arrival.accept.03</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>arrival.accept.04</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>arrival.accept.04</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>兴奋</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>arrival.accept.05</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>arrival.accept.05</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>开心</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>arrival.accept.06</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>arrival.accept.06</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>arrival.accept.07</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>arrival.accept.07</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>arrival.accept.08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>arrival.accept.08</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>arrival.accept.09</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>arrival.accept.09</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>arrival.accept.10</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>arrival.accept.10</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>迷惑</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>arrival.accept.11</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>arrival.accept.11</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>arrival.accept.12</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>arrival.accept.page</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>arrival.accept.12</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9920,7 +11749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10090,6 +11919,23 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>首日顾客B；知觉达到3触发成功支线</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>arrival.perception</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>arrival.insight</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>arrival.request</t>
         </is>
       </c>
     </row>
@@ -10104,7 +11950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10278,6 +12124,32 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>arrival.perception.1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>arrival.perception</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>perception</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10479,8 +12351,6 @@
           <t>first_day_cafe</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>customer_arrives</t>
@@ -10506,8 +12376,6 @@
           <t>cafe_tutorial.customer_arrives</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>perception_check</t>
@@ -10533,8 +12401,6 @@
           <t>cafe_tutorial.perception_success</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>order_confirmed</t>
@@ -10560,8 +12426,6 @@
           <t>cafe_tutorial.perception_failure</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>order_confirmed</t>
@@ -10587,8 +12451,6 @@
           <t>cafe_tutorial.order_confirmed</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>workstation_open</t>
@@ -10654,7 +12516,6 @@
           <t>cafe.coffee_base</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>pour_into_cup</t>
@@ -10685,7 +12546,6 @@
           <t>cafe.cup</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>adjust_strength</t>
@@ -10716,7 +12576,6 @@
           <t>cafe.strength</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>adjust_sweetness</t>
@@ -10747,7 +12606,6 @@
           <t>cafe.sweetness</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>serve_customer</t>
@@ -10773,9 +12631,6 @@
           <t>cafe_tutorial.demo_grind</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="b">
         <v>1</v>
       </c>
@@ -10796,9 +12651,6 @@
           <t>cafe_tutorial.demo_boil</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="b">
         <v>1</v>
       </c>
@@ -10819,9 +12671,6 @@
           <t>cafe_tutorial.demo_brew</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="b">
         <v>1</v>
       </c>
@@ -10842,9 +12691,6 @@
           <t>cafe_tutorial.demo_cup</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="b">
         <v>1</v>
       </c>
@@ -10865,9 +12711,6 @@
           <t>cafe_tutorial.demo_base</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="b">
         <v>1</v>
       </c>
@@ -10888,9 +12731,6 @@
           <t>cafe_tutorial.demo_strength</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="b">
         <v>1</v>
       </c>
@@ -10911,9 +12751,6 @@
           <t>cafe_tutorial.demo_sweetness</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="b">
         <v>1</v>
       </c>
@@ -10934,9 +12771,6 @@
           <t>cafe_tutorial.demo_serve</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="b">
         <v>1</v>
       </c>
@@ -10962,7 +12796,6 @@
           <t>cafe.delivery</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>result</t>
@@ -10988,8 +12821,6 @@
           <t>cafe_tutorial.result_excellent</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>ending</t>
@@ -11015,8 +12846,6 @@
           <t>cafe_tutorial.result_good</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>ending</t>
@@ -11042,8 +12871,6 @@
           <t>cafe_tutorial.result_average</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>ending</t>
@@ -11069,8 +12896,6 @@
           <t>cafe_tutorial.result_bad</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>ending</t>
@@ -11096,8 +12921,6 @@
           <t>cafe_tutorial.result_refund</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>make_coffee_base</t>
@@ -11123,9 +12946,6 @@
           <t>cafe_tutorial.ending</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="b">
         <v>0</v>
       </c>
@@ -12013,7 +13833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13865,6 +15685,446 @@
         <is>
           <t>FIRST_DAY_PERCEPTION</t>
         </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>arrival.start</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>arrival.start</t>
+        </is>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>arrival.start</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>arrival.reply.1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>arrival.reply.1</t>
+        </is>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>arrival.reply.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>arrival.reply.2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>arrival.reply.2</t>
+        </is>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>arrival.reply.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>arrival.agent</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>arrival.agent</t>
+        </is>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>arrival.agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>arrival.check</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>arrival.check</t>
+        </is>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>arrival.insight</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>arrival.insight</t>
+        </is>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>arrival.insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>arrival.request</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>arrival.request</t>
+        </is>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>arrival.request</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>arrival.decision</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>arrival.decision</t>
+        </is>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>arrival.decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>arrival.refuse</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>arrival.refuse</t>
+        </is>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>arrival.refuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>arrival.leave</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>arrival.accept</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>arrival.accept</t>
+        </is>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>arrival.accept</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>arrival.complete</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14076,7 +16336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16222,6 +18482,318 @@
           <t>示例阶段反馈可查看条件</t>
         </is>
       </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>arrival.reply.1.next</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>arrival.reply.1</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>arrival.agent</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>arrival.reply.2.next</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>arrival.reply.2</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>arrival.agent</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.1.next</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.1</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>arrival.reply.1</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.2.next</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.2</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>arrival.reply.2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>arrival.agent.next</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>arrival.agent</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>arrival.check</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>arrival.insight.next</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>arrival.insight</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>arrival.request</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>arrival.request.next</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>arrival.request</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>arrival.decision</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.1.next</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.1</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>arrival.refuse</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.2.next</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.2</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>arrival.accept</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.1.next</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.1</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>arrival.decision</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.2.next</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.2</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>arrival.leave</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>arrival.accept.next</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>arrival.accept</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>QUEUE_EVENT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>arrival.complete</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17620,7 +20192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18314,6 +20886,11 @@
           <t>Tpl_Narration</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>checkDisplay=passive</t>
+        </is>
+      </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
@@ -18359,6 +20936,211 @@
         <v>0</v>
       </c>
       <c r="F29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>arrival.start</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tpl_TwoPersonTalk</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>opts=MA70.10.06-S1-1</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>arrival.reply.1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tpl_TwoPersonTalk</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>arrival.reply.2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tpl_TwoPersonTalk</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>arrival.agent</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tpl_TwoPersonTalk</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>arrival.check</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tpl_Narration</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>checkDisplay=passive</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>arrival.perception</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>arrival.insight</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tpl_TwoPersonTalk</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>arrival.request</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tpl_TwoPersonTalk</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>arrival.decision</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tpl_TwoPersonTalk</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>opts=MA70.10.06-S1-2</t>
+        </is>
+      </c>
+      <c r="E37" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>arrival.refuse</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tpl_TwoPersonTalk</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>opts=MA70.10.06-S1-3</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>arrival.accept</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tpl_TwoPersonTalk</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -5988,7 +5988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6257,7 +6257,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.street</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6268,121 +6268,152 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MA70.10.06-S1-1</t>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/city_map_placeholder</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>arrival.reply.1.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>arrival.reply.1</t>
+          <t>arrival.start</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/city_map_placeholder</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>arrival.reply.2.page</t>
+          <t>arrival.reply.1.page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>arrival.reply.2</t>
+          <t>arrival.reply.1</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/phase_pre_business</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>arrival.agent.page</t>
+          <t>arrival.reply.2.page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>arrival.agent</t>
+          <t>arrival.reply.2</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/phase_pre_business</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>arrival.insight.page</t>
+          <t>arrival.agent.page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>arrival.insight</t>
+          <t>arrival.agent</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/phase_pre_business</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>arrival.request.page</t>
+          <t>arrival.insight.page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>arrival.request</t>
+          <t>arrival.insight</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/phase_pre_business</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>arrival.decision.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>arrival.decision</t>
+          <t>arrival.request</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MA70.10.06-S1-2</t>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/phase_pre_business</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.decision.page</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>arrival.refuse</t>
+          <t>arrival.decision</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -6390,25 +6421,81 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MA70.10.06-S1-3</t>
+          <t>MA70.10.06-S1-2</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/phase_pre_business</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>arrival.refuse</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/phase_pre_business</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>arrival.accept.welcome</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>arrival.accept</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/phase_pre_business</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>arrival.accept.malice</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>arrival.accept</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Art/Gameplay/DayFlow/phase_night_choice</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6421,7 +6508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6855,12 +6942,12 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>arrival.start.01</t>
+          <t>arrival.start.01.01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.street</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -6874,7 +6961,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>arrival.start.01</t>
+          <t>arrival.start.01.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -6882,12 +6969,12 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>arrival.start.02</t>
+          <t>arrival.start.01.02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.street</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -6901,7 +6988,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>arrival.start.02</t>
+          <t>arrival.start.01.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -6909,12 +6996,12 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>arrival.start.03</t>
+          <t>arrival.start.01.03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.street</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -6928,7 +7015,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>arrival.start.03</t>
+          <t>arrival.start.01.03</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -6936,12 +7023,12 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>arrival.start.04</t>
+          <t>arrival.start.01.04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.street</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -6955,7 +7042,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>arrival.start.04</t>
+          <t>arrival.start.01.04</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -6963,16 +7050,16 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>arrival.start.05</t>
+          <t>arrival.start.02.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
@@ -6982,7 +7069,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>arrival.start.05</t>
+          <t>arrival.start.02.01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -6990,16 +7077,16 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>arrival.start.06</t>
+          <t>arrival.start.02.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
@@ -7009,7 +7096,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>arrival.start.06</t>
+          <t>arrival.start.02.02</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -7017,16 +7104,16 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>arrival.start.07</t>
+          <t>arrival.start.02.03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
@@ -7036,7 +7123,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>arrival.start.07</t>
+          <t>arrival.start.02.03</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -7044,16 +7131,16 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>arrival.start.08</t>
+          <t>arrival.start.02.04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
@@ -7063,7 +7150,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>arrival.start.08</t>
+          <t>arrival.start.02.04</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -7071,16 +7158,16 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>arrival.start.09</t>
+          <t>arrival.start.02.05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
@@ -7090,7 +7177,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>arrival.start.09</t>
+          <t>arrival.start.02.05</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -7098,16 +7185,16 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>arrival.start.10</t>
+          <t>arrival.start.02.06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -7121,7 +7208,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>arrival.start.10</t>
+          <t>arrival.start.02.06</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -7129,144 +7216,144 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>arrival.start.11</t>
+          <t>arrival.start.02.07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>adele</t>
+          <t>player</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>arrival.start.11</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>平静</t>
-        </is>
-      </c>
+          <t>arrival.start.02.07</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>arrival.start.12</t>
+          <t>arrival.start.02.08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>adele</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>arrival.start.12</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>arrival.start.02.08</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>平静</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>arrival.start.13</t>
+          <t>arrival.start.02.09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arrival.start.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>adele</t>
+          <t>player</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>arrival.start.13</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>开心</t>
-        </is>
-      </c>
+          <t>arrival.start.02.09</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>arrival.reply.1.01</t>
+          <t>arrival.start.02.10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>arrival.reply.1.page</t>
+          <t>arrival.start.cafe</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>adele</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>arrival.reply.1.01</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>arrival.start.02.10</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>开心</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>arrival.reply.2.01</t>
+          <t>arrival.reply.1.01.01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>arrival.reply.2.page</t>
+          <t>arrival.reply.1.page</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -7284,7 +7371,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>arrival.reply.2.01</t>
+          <t>arrival.reply.1.01.01</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -7292,12 +7379,12 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>arrival.agent.01</t>
+          <t>arrival.reply.2.01.01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>arrival.agent.page</t>
+          <t>arrival.reply.2.page</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -7305,29 +7392,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>adele</t>
+          <t>player</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>arrival.agent.01</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>尴尬</t>
-        </is>
-      </c>
+          <t>arrival.reply.2.01.01</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>arrival.agent.02</t>
+          <t>arrival.agent.01.01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7336,7 +7419,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -7350,19 +7433,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>arrival.agent.02</t>
+          <t>arrival.agent.01.01</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>平静</t>
+          <t>尴尬</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>arrival.agent.03</t>
+          <t>arrival.agent.01.02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7371,29 +7454,33 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>adele</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>arrival.agent.03</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>arrival.agent.01.02</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>平静</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>arrival.agent.04</t>
+          <t>arrival.agent.01.03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7402,87 +7489,83 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>adele</t>
+          <t>player</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>arrival.agent.04</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>思索</t>
-        </is>
-      </c>
+          <t>arrival.agent.01.03</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>arrival.insight.01</t>
+          <t>arrival.agent.01.04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>arrival.insight.page</t>
+          <t>arrival.agent.page</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>adele</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>arrival.insight.01</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>arrival.agent.01.04</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>思索</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>arrival.request.01</t>
+          <t>arrival.agent.01.05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>arrival.request.page</t>
+          <t>arrival.agent.page</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>arrival.request.01</t>
+          <t>arrival.agent.01.05</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -7490,16 +7573,16 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>arrival.request.02</t>
+          <t>arrival.agent.01.06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>arrival.request.page</t>
+          <t>arrival.agent.page</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -7513,30 +7596,34 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>arrival.request.02</t>
+          <t>arrival.agent.01.06</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>悲伤</t>
+          <t>思索</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>arrival.request.03</t>
+          <t>arrival.agent.01.07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>arrival.request.page</t>
+          <t>arrival.agent.page</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>right</t>
@@ -7544,69 +7631,73 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>arrival.request.03</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>arrival.agent.01.07</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>思索</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>arrival.request.04</t>
+          <t>arrival.insight.01.01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>arrival.request.page</t>
+          <t>arrival.insight.page</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>adele</t>
+          <t>player</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>arrival.request.04</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>焦虑</t>
-        </is>
-      </c>
+          <t>arrival.insight.01.01</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>arrival.decision.01</t>
+          <t>arrival.request.01.01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>arrival.decision.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>arrival.decision.01</t>
+          <t>arrival.request.01.01</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -7614,18 +7705,22 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>arrival.refuse.01</t>
+          <t>arrival.request.01.02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>right</t>
@@ -7633,24 +7728,28 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>arrival.refuse.01</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>arrival.request.01.02</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>悲伤</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>arrival.refuse.02</t>
+          <t>arrival.request.01.03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
@@ -7660,7 +7759,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>arrival.refuse.02</t>
+          <t>arrival.request.01.03</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -7668,18 +7767,22 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>arrival.refuse.03</t>
+          <t>arrival.request.01.04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>right</t>
@@ -7687,24 +7790,28 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>arrival.refuse.03</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>arrival.request.01.04</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>悲伤</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>arrival.refuse.04</t>
+          <t>arrival.request.01.05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
@@ -7714,7 +7821,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>arrival.refuse.04</t>
+          <t>arrival.request.01.05</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -7722,18 +7829,22 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>arrival.refuse.05</t>
+          <t>arrival.request.01.06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>right</t>
@@ -7741,24 +7852,28 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>arrival.refuse.05</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>arrival.request.01.06</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>焦虑</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>arrival.refuse.06</t>
+          <t>arrival.request.01.07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
@@ -7768,7 +7883,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>arrival.refuse.06</t>
+          <t>arrival.request.01.07</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -7776,18 +7891,22 @@
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>arrival.refuse.07</t>
+          <t>arrival.request.01.08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>right</t>
@@ -7795,26 +7914,34 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>arrival.refuse.07</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>arrival.request.01.08</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>焦虑</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>arrival.refuse.08</t>
+          <t>arrival.request.01.09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.request.page</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>right</t>
@@ -7822,24 +7949,28 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>arrival.refuse.08</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>arrival.request.01.09</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>焦虑</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>arrival.refuse.09</t>
+          <t>arrival.decision.01.01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>arrival.refuse.page</t>
+          <t>arrival.decision.page</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
@@ -7849,7 +7980,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>arrival.refuse.09</t>
+          <t>arrival.decision.01.01</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -7857,30 +7988,26 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>arrival.accept.01</t>
+          <t>arrival.refuse.01.01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>arrival.accept.01</t>
+          <t>arrival.refuse.01.01</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -7888,22 +8015,18 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>arrival.accept.02</t>
+          <t>arrival.refuse.01.02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>adele</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>right</t>
@@ -7911,42 +8034,34 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>arrival.accept.02</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>迷惑</t>
-        </is>
-      </c>
+          <t>arrival.refuse.01.02</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>arrival.accept.03</t>
+          <t>arrival.refuse.01.03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>3</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>arrival.accept.03</t>
+          <t>arrival.refuse.01.03</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -7954,22 +8069,18 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>arrival.accept.04</t>
+          <t>arrival.refuse.01.04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>4</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>adele</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>right</t>
@@ -7977,34 +8088,26 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>arrival.accept.04</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>兴奋</t>
-        </is>
-      </c>
+          <t>arrival.refuse.01.04</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>arrival.accept.05</t>
+          <t>arrival.refuse.01.05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>5</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>adele</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>right</t>
@@ -8012,24 +8115,20 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>arrival.accept.05</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>开心</t>
-        </is>
-      </c>
+          <t>arrival.refuse.01.05</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>arrival.accept.06</t>
+          <t>arrival.refuse.01.06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -8043,7 +8142,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>arrival.accept.06</t>
+          <t>arrival.refuse.01.06</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -8051,12 +8150,12 @@
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>arrival.accept.07</t>
+          <t>arrival.refuse.01.07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -8070,7 +8169,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>arrival.accept.07</t>
+          <t>arrival.refuse.01.07</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -8078,12 +8177,12 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>arrival.accept.08</t>
+          <t>arrival.refuse.01.08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -8097,7 +8196,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>arrival.accept.08</t>
+          <t>arrival.refuse.01.08</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -8105,12 +8204,12 @@
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>arrival.accept.09</t>
+          <t>arrival.refuse.01.09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.refuse.page</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -8124,7 +8223,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>arrival.accept.09</t>
+          <t>arrival.refuse.01.09</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -8132,95 +8231,432 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>arrival.accept.10</t>
+          <t>arrival.accept.01.01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.accept.welcome</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>adele</t>
+          <t>player</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>arrival.accept.10</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>迷惑</t>
-        </is>
-      </c>
+          <t>arrival.accept.01.01</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>arrival.accept.11</t>
+          <t>arrival.accept.01.02</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.accept.welcome</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>adele</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>arrival.accept.11</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>arrival.accept.01.02</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>迷惑</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>arrival.accept.12</t>
+          <t>arrival.accept.01.03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>arrival.accept.page</t>
+          <t>arrival.accept.welcome</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.03</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.04</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>arrival.accept.welcome</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>right</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>arrival.accept.12</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.04</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>兴奋</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.05</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>arrival.accept.welcome</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.05</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.06</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>arrival.accept.welcome</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.06</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>兴奋</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.07</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>arrival.accept.welcome</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.07</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>开心</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.08</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>arrival.accept.welcome</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.08</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>arrival.accept.malice</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.01</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.02</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>arrival.accept.malice</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.02</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>arrival.accept.malice</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.03</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.04</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>arrival.accept.malice</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>adele</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.04</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>迷惑</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.05</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>arrival.accept.malice</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.05</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.06</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>arrival.accept.malice</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.06</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18504,7 +18940,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>arrival.agent</t>
+          <t>event:arrival.agent</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -18530,7 +18966,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>arrival.agent</t>
+          <t>event:arrival.agent</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -18556,7 +18992,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>arrival.reply.1</t>
+          <t>event:arrival.reply.1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -18582,7 +19018,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>arrival.reply.2</t>
+          <t>event:arrival.reply.2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -18608,7 +19044,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>arrival.check</t>
+          <t>event:arrival.check</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -18634,7 +19070,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>arrival.request</t>
+          <t>event:arrival.request</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -18660,7 +19096,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>arrival.decision</t>
+          <t>event:arrival.decision</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -18686,7 +19122,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>arrival.refuse</t>
+          <t>event:arrival.refuse</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -18712,7 +19148,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>arrival.accept</t>
+          <t>event:arrival.accept</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -18738,7 +19174,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>arrival.decision</t>
+          <t>event:arrival.decision</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -18764,7 +19200,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>arrival.leave</t>
+          <t>event:arrival.leave</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -18790,7 +19226,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>arrival.complete</t>
+          <t>event:arrival.complete</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -19742,7 +20178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20178,6 +20614,92 @@
         </is>
       </c>
       <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tpl_ArrivalConversation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>抵达剧情分页</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>progressive</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>A_DIALOG,A_CHOICE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>opts:optionList</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tpl_PassiveCheck</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>静默属性检定</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>progressive</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>A_NARRATE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>checkDisplay:text</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tpl_NarrativeSignal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>无正文流程通知</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>progressive</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>A_NARRATE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20883,7 +21405,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tpl_Narration</t>
+          <t>Tpl_PassiveCheck</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -20911,9 +21433,10 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tpl_Narration</t>
-        </is>
-      </c>
+          <t>Tpl_NarrativeSignal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="b">
         <v>0</v>
       </c>
@@ -20929,9 +21452,10 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tpl_Narration</t>
-        </is>
-      </c>
+          <t>Tpl_NarrativeSignal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="b">
         <v>0</v>
       </c>
@@ -20947,7 +21471,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tpl_TwoPersonTalk</t>
+          <t>Tpl_ArrivalConversation</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -20970,10 +21494,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tpl_TwoPersonTalk</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Tpl_ArrivalConversation</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>opts=</t>
+        </is>
+      </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
@@ -20989,10 +21517,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tpl_TwoPersonTalk</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Tpl_ArrivalConversation</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>opts=</t>
+        </is>
+      </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
@@ -21008,10 +21540,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tpl_TwoPersonTalk</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Tpl_ArrivalConversation</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>opts=</t>
+        </is>
+      </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
@@ -21027,7 +21563,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tpl_Narration</t>
+          <t>Tpl_PassiveCheck</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -21049,10 +21585,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tpl_TwoPersonTalk</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Tpl_ArrivalConversation</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>opts=</t>
+        </is>
+      </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
@@ -21068,10 +21608,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tpl_TwoPersonTalk</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Tpl_ArrivalConversation</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>opts=</t>
+        </is>
+      </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
@@ -21087,7 +21631,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tpl_TwoPersonTalk</t>
+          <t>Tpl_ArrivalConversation</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -21110,7 +21654,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tpl_TwoPersonTalk</t>
+          <t>Tpl_ArrivalConversation</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -21133,10 +21677,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tpl_TwoPersonTalk</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Tpl_ArrivalConversation</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>opts=</t>
+        </is>
+      </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -1234,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1658,22 +1658,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Characters/adele/avatar</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Characters/adele/neutral</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Characters/adele/neutral</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Characters/adele/neutral</t>
+          <t>Characters/adele/seated_placeholder</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Characters/adele/neutral</t>
+          <t>Characters/adele/avatar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1860,6 +1860,1463 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>church.man.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>laurent</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>character.laurent.name</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Characters/laurent/avatar</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Characters/laurent/neutral</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Characters/laurent/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Characters/laurent/avatar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>character.laurent.desc</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>noble,auditor,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>clovis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>character.clovis.name</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Characters/clovis/avatar</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Characters/clovis/neutral</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Characters/clovis/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Characters/clovis/avatar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>character.clovis.desc</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>noble,king,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>renaud</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>character.renaud.name</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Characters/renaud/avatar</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Characters/renaud/neutral</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Characters/renaud/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Characters/renaud/avatar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>character.renaud.desc</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>noble,duke,royal_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>elion</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>character.elion.name</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Characters/elion/avatar</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Characters/elion/neutral</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Characters/elion/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Characters/elion/avatar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>character.elion.desc</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>noble,duke,crown,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>alienor</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>character.alienor.name</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Characters/alienor/avatar</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Characters/alienor/neutral</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Characters/alienor/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Characters/alienor/avatar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>character.alienor.desc</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>noble,princess,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>character.queen.name</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Characters/queen/avatar</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Characters/queen/neutral</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Characters/queen/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Characters/queen/avatar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>character.queen.desc</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>noble,queen,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bertrand</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>character.bertrand.name</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Characters/bertrand/avatar</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Characters/bertrand/neutral</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Characters/bertrand/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Characters/bertrand/avatar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>character.bertrand.desc</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>noble</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sade</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>character.sade.name</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Characters/sade/avatar</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Characters/sade/neutral</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Characters/sade/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Characters/sade/avatar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>character.sade.desc</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>church,priest,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>mamion</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>character.mamion.name</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Characters/mamion/avatar</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Characters/mamion/neutral</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Characters/mamion/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Characters/mamion/avatar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>character.mamion.desc</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>church,archbishop</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>lucien</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>character.lucien.name</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Characters/lucien/avatar</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Characters/lucien/neutral</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Characters/lucien/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Characters/lucien/avatar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>character.lucien.desc</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>church,priest</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>lesou</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>character.lesou.name</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Characters/lesou/avatar</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Characters/lesou/neutral</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Characters/lesou/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Characters/lesou/avatar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>character.lesou.desc</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>refugee,revolution,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sylvain</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>character.sylvain.name</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Characters/sylvain/avatar</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Characters/sylvain/neutral</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Characters/sylvain/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Characters/sylvain/avatar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>character.sylvain.desc</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>scholar,historian</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>antoine</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>character.antoine.name</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Characters/antoine/avatar</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Characters/antoine/neutral</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Characters/antoine/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Characters/antoine/avatar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>character.antoine.desc</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>merchant,citizen,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>lefebvre</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>character.lefebvre.name</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Characters/lefebvre/avatar</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Characters/lefebvre/neutral</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Characters/lefebvre/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Characters/lefebvre/avatar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>character.lefebvre.desc</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>official,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>duval</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>character.duval.name</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Characters/duval/avatar</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Characters/duval/neutral</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Characters/duval/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Characters/duval/avatar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>character.duval.desc</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>citizen,uncle</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>emmanuel</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>character.emmanuel.name</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Characters/emmanuel/avatar</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Characters/emmanuel/neutral</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Characters/emmanuel/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Characters/emmanuel/avatar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>character.emmanuel.desc</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>citizen,surgeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sparrow</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>character.sparrow.name</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Characters/sparrow/avatar</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Characters/sparrow/neutral</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Characters/sparrow/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Characters/sparrow/avatar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>character.sparrow.desc</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>citizen,street_youth</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>thibaut</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>character.thibaut.name</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Characters/thibaut/avatar</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Characters/thibaut/neutral</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Characters/thibaut/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Characters/thibaut/avatar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>character.thibaut.desc</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>veteran,informant,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>octave</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>character.octave.name</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Characters/octave/avatar</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Characters/octave/neutral</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Characters/octave/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Characters/octave/avatar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>character.octave.desc</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>military,general</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>eugene</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>character.eugene.name</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Characters/eugene/avatar</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Characters/eugene/neutral</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Characters/eugene/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Characters/eugene/avatar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>character.eugene.desc</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>veteran,bodyguard,cafe_customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>character.colette.name</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Characters/colette/avatar</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Characters/colette/neutral</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Characters/colette/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Characters/colette/avatar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>character.colette.desc</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>citizen,cafe_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>character.pascal.name</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Characters/pascal/avatar</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Characters/pascal/neutral</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Characters/pascal/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Characters/pascal/avatar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>character.pascal.desc</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>citizen,printer,cafe_staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>marie</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>character.marie.name</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Characters/marie/avatar</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Characters/marie/neutral</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Characters/marie/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Characters/marie/avatar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>character.marie.desc</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>citizen,former_manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>guest_a</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>character.guest_a.name</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Characters/guest_a/avatar</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Characters/guest_a/neutral</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Characters/guest_a/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Characters/guest_a/avatar</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>character.guest_a.desc</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>refugee,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>guest_b</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>character.guest_b.name</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Characters/guest_b/avatar</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Characters/guest_b/neutral</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Characters/guest_b/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Characters/guest_b/avatar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>character.guest_b.desc</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>citizen,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>guest_c</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>character.guest_c.name</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Characters/guest_c/avatar</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Characters/guest_c/neutral</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Characters/guest_c/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Characters/guest_c/avatar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>character.guest_c.desc</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>church,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>guest_d</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>character.guest_d.name</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Characters/guest_d/avatar</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Characters/guest_d/neutral</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Characters/guest_d/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Characters/guest_d/avatar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>character.guest_d.desc</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>crown,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>soldier_a</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>character.soldier_a.name</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Characters/soldier_a/avatar</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Characters/soldier_a/neutral</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Characters/soldier_a/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Characters/soldier_a/avatar</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>character.soldier_a.desc</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>revolution,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>soldier_b</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>character.soldier_b.name</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Characters/soldier_b/avatar</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Characters/soldier_b/neutral</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Characters/soldier_b/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Characters/soldier_b/avatar</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>character.soldier_b.desc</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>military,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>soldier_c</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>character.soldier_c.name</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Characters/soldier_c/avatar</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Characters/soldier_c/neutral</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Characters/soldier_c/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Characters/soldier_c/avatar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>character.soldier_c.desc</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>royal_guard,generic</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>soldier_d</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>character.soldier_d.name</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Characters/soldier_d/avatar</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Characters/soldier_d/neutral</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Characters/soldier_d/seated_placeholder</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Characters/soldier_d/avatar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>character.soldier_d.desc</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>new_rose,generic</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -1234,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3320,6 +3320,60 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>neutral.1008.shopkeeper</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>character.market.shopkeeper.name</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>character.market.shopkeeper.desc</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>neutral,a01,shopkeeper</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>neutral.1008.unknown</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>character.neutral.1008.unknown.name</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>character.neutral.1008.unknown.desc</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>neutral,a01,anonymous</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -3332,7 +3386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4187,6 +4241,71 @@
       </c>
       <c r="F36" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.choice.q1.a</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.q1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p036</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.choice.q1.b</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.q1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p037</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.q1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.choice.q1.c</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.q1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p038</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4374,7 +4493,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4406,7 +4525,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4438,7 +4557,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4470,7 +4589,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4502,7 +4621,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4534,7 +4653,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4566,7 +4685,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4598,7 +4717,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4630,7 +4749,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4662,7 +4781,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4694,7 +4813,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4726,7 +4845,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4758,7 +4877,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4790,7 +4909,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4822,7 +4941,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4854,7 +4973,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4886,7 +5005,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4918,7 +5037,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4950,7 +5069,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4982,7 +5101,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -5014,7 +5133,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5046,7 +5165,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -5078,7 +5197,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5110,7 +5229,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5142,7 +5261,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dialogue/CafeSceneVisuals</t>
+          <t>Dialogue/FirstDayIntroductionVisuals</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7423,7 +7542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7961,6 +8080,107 @@
         <v>1</v>
       </c>
       <c r="N9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.action</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ONCE</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>action.neutral.1008.s1.name</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>action.neutral.1008.s1.desc</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.action</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ONCE</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>action.rose.1009.s1.name</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>action.rose.1009.s1.desc</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ActionPoint(1)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>rose.1009.s1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8241,6 +8461,11 @@
       <c r="F6" t="b">
         <v>1</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.action</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Art/Map/Locations/location_05</t>
@@ -8356,6 +8581,11 @@
       </c>
       <c r="F10" t="b">
         <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.action</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8465,7 +8695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8961,6 +9191,23 @@
       <c r="D28" t="inlineStr">
         <is>
           <t>D1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NEUTRAL_1008_S1</t>
         </is>
       </c>
     </row>
@@ -8975,7 +9222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9552,7 +9799,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9839,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -9617,7 +9864,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -9647,7 +9894,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -9672,7 +9919,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -9702,7 +9949,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -9727,7 +9974,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -9757,7 +10004,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -9907,7 +10154,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -9937,7 +10184,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -9967,7 +10214,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -9997,7 +10244,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -10022,7 +10269,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -10047,7 +10294,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -10072,7 +10319,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -10102,7 +10349,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -10127,7 +10374,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -10157,7 +10404,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -10187,7 +10434,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -10217,7 +10464,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -10247,7 +10494,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -10272,7 +10519,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -10297,7 +10544,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -10327,7 +10574,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.night</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -10357,7 +10604,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -10382,7 +10629,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -10412,7 +10659,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -10442,7 +10689,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -10472,7 +10719,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -10497,7 +10744,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -10532,7 +10779,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -10562,7 +10809,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -10592,7 +10839,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -10622,7 +10869,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -10652,7 +10899,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -10687,7 +10934,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -10717,7 +10964,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -10747,7 +10994,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -10777,7 +11024,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -10807,7 +11054,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -10837,7 +11084,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -10862,7 +11109,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -10897,7 +11144,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -10922,7 +11169,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -10947,7 +11194,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -10972,7 +11219,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -11002,7 +11249,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>scene.cafe</t>
+          <t>oct07.cafe.day</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -11128,6 +11375,186 @@
       <c r="J78" t="inlineStr">
         <is>
           <t>Dialogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.market</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>neutral.market.day</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>neutral.market.shop.day</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.q1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.help</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>choice:neutral.1008.s1.choice.q1.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.talk_pass</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>choice:neutral.1008.s1.choice.q1.b|check:neutral.1008.s1.q1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.talk_fail</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>choice:neutral.1008.s1.choice.q1.b|not:check:neutral.1008.s1.q1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.wait</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>7</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>choice:neutral.1008.s1.choice.q1.c</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>8</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>neutral.market.shop.day</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.outro</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>9</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>neutral.market.day</t>
         </is>
       </c>
     </row>
@@ -11143,7 +11570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M606"/>
+  <dimension ref="A1:M666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29131,6 +29558,1806 @@
       <c r="G606" t="inlineStr">
         <is>
           <t>church.1009.s2.p050.text</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p004</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.market</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>1</v>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p004</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p005</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.market</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>2</v>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p005</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p006</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.market</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>3</v>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p006</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p008</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.market</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>4</v>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p008</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p009</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.market</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>5</v>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p009</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p010</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.market</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>6</v>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p010</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p011</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.market</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>7</v>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p011</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p014</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>1</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p014</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p015</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>2</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>neutral.1008.shopkeeper</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p015</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p016</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>3</v>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p016</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p017</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>4</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>neutral.1008.shopkeeper</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p017</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p018</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>5</v>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>neutral.1008.unknown</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p018</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p020</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>6</v>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>neutral.1008.unknown</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p020</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p021</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>7</v>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p021</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p023</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>8</v>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p023</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>flustered</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p024</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>9</v>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p024</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p025</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>10</v>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p025</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p026</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>11</v>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p026</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p027</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>12</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p027</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>muttering</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p028</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>13</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>neutral.1008.shopkeeper</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p028</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p029</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>14</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p029</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>defiant</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p030</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>15</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>neutral.1008.shopkeeper</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p030</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p031</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>16</v>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p031</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p032</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>17</v>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p032</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p034</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.shop</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>18</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p034</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>strained</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p040</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.help</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>1</v>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p040</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p041</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.help</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>2</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p041</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p042</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.help</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>3</v>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p042</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p044</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.help</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>4</v>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p044</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p048</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.talk_pass</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>1</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p048</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p049</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.talk_pass</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>2</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p049</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p053</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.talk_fail</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>1</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p053</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p054</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.talk_fail</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>2</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p054</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>embarrassed</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p056</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.wait</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>1</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p056</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p057</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.wait</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>2</v>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p057</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>apologetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p058</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.wait</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>3</v>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>neutral.1008.shopkeeper</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p058</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p059</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.wait</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>4</v>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p059</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p060</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>1</v>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p060</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p061</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>2</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p061</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p062</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>3</v>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p062</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p063</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>4</v>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p063</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p064</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>5</v>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p064</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p065</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>6</v>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p065</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p066</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>7</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p066</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p067</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>8</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p067</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p068</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>9</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p068</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p069</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>10</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p069</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>proud</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p070</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>11</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p070</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p071</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>12</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p071</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p072</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>13</v>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p072</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p073</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>14</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p073</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p074</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>15</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p074</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p075</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>16</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p075</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p076</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>17</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p076</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p077</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>18</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p077</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p078</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>19</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>colette</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p078</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p080</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.join</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>20</v>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p080</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p083</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.outro</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>1</v>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p083</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p084</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.outro</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>2</v>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p084</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.line.p085</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.outro</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>3</v>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.text.p085</t>
         </is>
       </c>
     </row>
@@ -31515,7 +33742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32145,6 +34372,43 @@
         <v>0</v>
       </c>
       <c r="E33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>story.neutral.1008.s1.completed</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1008.s1.completed</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>story.rose.1009.s1.completed</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>condition.story.rose.1009.s1.completed</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -33044,7 +35308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33317,6 +35581,23 @@
         </is>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>Inline</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.q1b</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>A01 q1.B; language &gt;= 2; choice remains selectable on failure.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Inline</t>
         </is>
@@ -33334,7 +35615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33638,6 +35919,32 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.q1b.1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.q1b</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -35321,7 +37628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37967,6 +40274,61 @@
       <c r="O60" t="inlineStr">
         <is>
           <t>entry=Immediate;blocksSave=true;blockedBy=D-B03-rose-real-completion</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>neutral.1008.shopkeeper</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.title</t>
+        </is>
+      </c>
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>NEUTRAL_1008_S1</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>NEUTRAL_1008_S1</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>entry=MapAction;blocksSave=true</t>
         </is>
       </c>
     </row>
@@ -38203,7 +40565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -40790,6 +43152,185 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.complete</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SET_FLAG</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>story.neutral.1008.s1.completed</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>A01 root completion; relation deltas await A-B010.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.complete</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>rose.1009.s1</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>SET_FLAG</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>story.rose.1009.s1.completed</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>完成 B-1009 赴约剧情后记录；不重复触发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>revolution.1013.s2.complete</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>revolution.1013.s2</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SET_FLAG</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>story.revolution.1013.s2.completed</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>C13 对话完整结束后记录剧情完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>revolution.1014.s1.complete</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>revolution.1014.s1</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SET_FLAG</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>story.revolution.1014.s1.completed</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>C14 对话完整结束后记录剧情完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>revolution.1028.s1.complete</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>revolution.1028.s1</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>SET_FLAG</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>story.revolution.1028.s1.completed</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>C28 对话完整结束后记录剧情完成。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40801,7 +43342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -42458,6 +44999,324 @@
         </is>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.day</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BAR_BETWEEN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>world.calendar</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.map</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BOOL_EQ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>world.map.active</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.incomplete</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BOOL_EQ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>story.neutral.1008.s1.completed</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.action.day</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.action</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BAR_BETWEEN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>world.calendar</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.action.map</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.action</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BOOL_EQ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>world.map.active</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.action.incomplete</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.action</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BOOL_EQ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>story.neutral.1008.s1.completed</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.action.day</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.action</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BAR_BETWEEN</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>world.calendar</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.action.meeting</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.action</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BOOL_EQ</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>story.oct09.meeting.known</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.action.incomplete</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.action</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BOOL_EQ</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>story.rose.1009.s1.completed</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>false</t>
         </is>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -8131,7 +8131,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>rose.1009.s1.action</t>
@@ -8171,7 +8170,6 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>None</t>
@@ -9105,7 +9103,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B1009 blocked P003-P071</t>
+          <t>B1009 P003-P076; temporary black CG placeholder pending B-R004 art</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11556,6 +11554,71 @@
         <is>
           <t>neutral.market.day</t>
         </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.portrait_cg</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.conversation</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>7</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>rose.club.knight_guidance</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PassiveCheck</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.perception</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.portrait_no_cg</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.conversation</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>not:check:rose.1009.s1.perception</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.portrait_tail</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.conversation</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -11570,7 +11633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M666"/>
+  <dimension ref="A1:M671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31358,6 +31421,131 @@
       <c r="G666" t="inlineStr">
         <is>
           <t>neutral.1008.s1.text.p085</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.p073.cg</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.portrait_cg</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>1</v>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.text.p073</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.p073.no_cg</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.portrait_no_cg</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>1</v>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.text.p073</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.p074</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.portrait_tail</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>1</v>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.text.p074</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.p075</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.portrait_tail</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>2</v>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.text.p075</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.p076</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.portrait_tail</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>3</v>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.text.p076</t>
         </is>
       </c>
     </row>
@@ -34394,7 +34582,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>story.rose.1009.s1.completed</t>
@@ -35308,7 +35495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35598,6 +35785,23 @@
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>Inline</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.perception</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>B1009 P072-P076; perception&gt;=5 shows the authored CG with P073. Failure keeps the same P073 text without CG. Both paths continue P074-P076 and complete the root.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Inline</t>
         </is>
@@ -35615,7 +35819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35945,6 +36149,32 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.perception.1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rose.1009.s1.perception</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>perception</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -40073,7 +40303,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>entry=MapAction;blocksSave=true;blockedBy=B-B01+B-B02;contentBoundary=P071</t>
+          <t>entry=MapAction;blocksSave=true;contentBoundary=P076</t>
         </is>
       </c>
     </row>
@@ -40223,7 +40453,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>entry=MorningBeforeMap;blocksSave=true;blockedBy=C-B03,C-B04,C-B05,B-real-completion,C-G02,C-G05,C-G07</t>
+          <t>entry=MorningBeforeMap;blocksSave=true;blockedBy=C-B03,C-B04,C-B05,B-real-completion,C-G02,C-G07</t>
         </is>
       </c>
     </row>
@@ -43188,7 +43418,6 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
           <t>rose.1009.s1.complete</t>
@@ -43224,7 +43453,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
           <t>revolution.1013.s2.complete</t>
@@ -43260,7 +43488,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>revolution.1014.s1.complete</t>
@@ -43296,7 +43523,6 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
           <t>revolution.1028.s1.complete</t>
@@ -45215,7 +45441,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>rose.1009.s1.action.day</t>
@@ -45251,7 +45476,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
           <t>rose.1009.s1.action.meeting</t>
@@ -45287,7 +45511,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
           <t>rose.1009.s1.action.incomplete</t>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -1,40 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Object" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Bar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Trigger" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Event" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="EventDate" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Result" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Condition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Template" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SetupParams" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Choice" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="OpeningPresentation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="OpeningLine" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Action" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="MapPosition" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="PresentationIndex" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ConversationPage" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ConversationLine" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Notice" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="ReadingPage" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="ReadingLine" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="ConditionKey" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="ActionMilestone" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Ending" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="CafeVisit" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="CafeVisitHook" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="AbilityCheck" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="AbilityCheckCondition" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="CafeTutorialStep" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Object" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trigger" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventDate" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Result" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condition" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SetupParams" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choice" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpeningPresentation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpeningLine" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPosition" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PresentationIndex" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConversationPage" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConversationLine" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notice" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadingPage" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadingLine" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConditionKey" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActionMilestone" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ending" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CafeVisit" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CafeVisitHook" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AbilityCheck" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AbilityCheckCondition" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CafeTutorialStep" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4538,12 +4538,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4565,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4602,7 +4597,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4634,7 +4629,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4666,7 +4661,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4698,12 +4693,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -4730,12 +4720,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -4762,12 +4747,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -4794,12 +4774,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4801,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4828,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4855,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -4922,12 +4882,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4909,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -4986,12 +4936,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -5018,12 +4963,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -5050,12 +4990,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5017,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5044,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5071,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -5178,7 +5103,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5210,7 +5135,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -5242,7 +5167,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5274,7 +5199,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5306,12 +5231,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>cafe.tutorial.customer.name</t>
+          <t>Dialogue/CafeTutorialVisuals</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative/Narrative.xlsx
@@ -1,40 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Object" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Bar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Trigger" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Event" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="EventDate" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Result" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Condition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Template" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SetupParams" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Choice" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="OpeningPresentation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="OpeningLine" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Action" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="MapPosition" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="PresentationIndex" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ConversationPage" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ConversationLine" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Notice" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="ReadingPage" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="ReadingLine" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="ConditionKey" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="ActionMilestone" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Ending" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="CafeVisit" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="CafeVisitHook" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="AbilityCheck" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="AbilityCheckCondition" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="CafeTutorialStep" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Object" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trigger" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventDate" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Result" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condition" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SetupParams" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choice" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpeningPresentation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpeningLine" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapPosition" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PresentationIndex" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConversationPage" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConversationLine" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notice" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadingPage" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadingLine" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConditionKey" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActionMilestone" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ending" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CafeVisit" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CafeVisitHook" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AbilityCheck" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AbilityCheckCondition" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CafeTutorialStep" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dialogue/FirstDayIntroductionVisuals</t>
+          <t>Dialogue/CafeSceneVisuals</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>oct07.cafe.night</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>oct07.cafe.day</t>
+          <t>scene.cafe</t>
         </is>
       </c>
     </row>
@@ -45799,7 +45799,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>entry=Immediate;blocksSave=true;blockedBy=C-B01,C-B02,C-B05,C-G04</t>
+          <t>entry=Immediate;blocksSave=true</t>
         </is>
       </c>
     </row>
@@ -45849,7 +45849,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>entry=BeforeNight;blocksSave=true;blockedBy=C-B05,C-B06,C-G07</t>
+          <t>entry=BeforeNight;blocksSave=true</t>
         </is>
       </c>
     </row>
@@ -45899,7 +45899,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>entry=MorningBeforeMap;blocksSave=true;blockedBy=C-B03,C-B04,C-B05,B-real-completion,C-G02,C-G07</t>
+          <t>entry=MorningBeforeMap;blocksSave=true</t>
         </is>
       </c>
     </row>
@@ -45949,7 +45949,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>entry=Immediate;blocksSave=true;blockedBy=D-B03-rose-real-completion</t>
+          <t>entry=Immediate;blocksSave=true</t>
         </is>
       </c>
     </row>
@@ -46059,7 +46059,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>entry=MorningBeforeMap;blocksSave=true;blockedBy=B-B05,B-C02,B-C04,B-C07;contentBoundary=P047;previewTail=P052</t>
+          <t>entry=MorningBeforeMap;blocksSave=true;contentBoundary=P047;previewTail=P052</t>
         </is>
       </c>
     </row>
@@ -46075,7 +46075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -46308,6 +46308,54 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>church.1009.s2</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>revolution.1013.s2</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>noon</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -46320,7 +46368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -47498,6 +47546,41 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>rose.1011.s1.complete</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>rose.1011.s1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SET_FLAG</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>story.rose.1011.s1.completed</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Formal root completion; commit only after full presentation and reading return.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47509,7 +47592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -48165,7 +48248,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>story.oct09.meeting.known</t>
+          <t>story.oct07.s2.completed</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -48830,7 +48913,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>story.oct09.meeting.known</t>
+          <t>story.oct07.s2.completed</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -48912,7 +48995,7 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>rose.1011.s1.neutral_ready</t>
+          <t>rose.1011.s1.rose1009_ready</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -48935,7 +49018,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>story.neutral.1010.s1.completed</t>
+          <t>story.rose.1009.s1.completed</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -48947,7 +49030,7 @@
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>rose.1011.s1.rose1009_ready</t>
+          <t>rose.1011.s1.incomplete</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -48970,19 +49053,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>story.rose.1009.s1.completed</t>
+          <t>story.rose.1011.s1.completed</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>rose.1011.s1.incomplete</t>
+          <t>church.1009.s2.rose1009_ready</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -48992,7 +49075,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>rose.1011.s1</t>
+          <t>church.1009.s2</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -49005,12 +49088,47 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>story.rose.1009.s1.completed</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>revolution.1014.s1.rose1011_ready</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>revolution.1014.s1</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BOOL_EQ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>story.rose.1011.s1.completed</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>false</t>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
